--- a/reconcile/storage/input/product_classification.xlsx
+++ b/reconcile/storage/input/product_classification.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjamin_mcwilliams/Documents/bruegel/data_new/WORKING/INDUSTRY/tuone_v6/reconcile/storage/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82D33E6-FDEE-B144-B885-F6D0839E06A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B49129-B8FA-6544-B0B7-DC7600C84D13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3891" uniqueCount="2200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3915" uniqueCount="2200">
   <si>
     <t>product</t>
   </si>
@@ -8398,6 +8398,12 @@
       <c r="A172" t="s">
         <v>182</v>
       </c>
+      <c r="B172" t="s">
+        <v>8</v>
+      </c>
+      <c r="C172" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
@@ -9216,6 +9222,12 @@
       <c r="A284" t="s">
         <v>294</v>
       </c>
+      <c r="B284" t="s">
+        <v>8</v>
+      </c>
+      <c r="C284" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
@@ -9292,6 +9304,9 @@
       <c r="B295" t="s">
         <v>8</v>
       </c>
+      <c r="C295" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
@@ -15974,26 +15989,56 @@
       <c r="A1200" t="s">
         <v>1213</v>
       </c>
+      <c r="B1200" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" t="s">
         <v>1214</v>
       </c>
+      <c r="B1201" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1202" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1202" t="s">
         <v>1215</v>
       </c>
+      <c r="B1202" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1203" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1203" t="s">
         <v>1216</v>
       </c>
+      <c r="B1203" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1204" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1204" t="s">
         <v>1217</v>
       </c>
+      <c r="B1204" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1205" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1205" t="s">
@@ -16009,6 +16054,12 @@
       <c r="A1207" t="s">
         <v>1220</v>
       </c>
+      <c r="B1207" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1208" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1208" t="s">
@@ -16292,11 +16343,23 @@
       <c r="A1248" t="s">
         <v>1261</v>
       </c>
+      <c r="B1248" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1249" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1249" t="s">
         <v>1262</v>
       </c>
+      <c r="B1249" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1250" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1250" t="s">
@@ -17780,6 +17843,12 @@
       <c r="A1446" t="s">
         <v>1459</v>
       </c>
+      <c r="B1446" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1446" t="s">
+        <v>562</v>
+      </c>
     </row>
     <row r="1447" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1447" t="s">
@@ -18341,6 +18410,9 @@
       </c>
       <c r="B1544" t="s">
         <v>8</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="1545" spans="1:3" x14ac:dyDescent="0.2">
